--- a/gce/dist/20261025_金像電模型_v0.1.1.xlsx
+++ b/gce/dist/20261025_金像電模型_v0.1.1.xlsx
@@ -6318,7 +6318,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6517,7 +6517,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6638,7 +6638,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6759,7 +6759,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6880,7 +6880,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7001,7 +7001,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/gce/dist/20261025_金像電模型_v0.1.1.xlsx
+++ b/gce/dist/20261025_金像電模型_v0.1.1.xlsx
@@ -5219,7 +5219,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5238,7 +5238,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/gce/dist/20261025_金像電模型_v0.1.1.xlsx
+++ b/gce/dist/20261025_金像電模型_v0.1.1.xlsx
@@ -5532,7 +5532,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -5551,7 +5551,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6012,7 +6012,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6031,7 +6031,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -42232,7 +42232,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>34</v>
@@ -45826,7 +45826,7 @@
       </c>
       <c r="C12" s="22" t="n">
         <f aca="false">PL!D116*PL!D118</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="D12" s="22" t="n">
         <f aca="false">PL!E116*PL!E118</f>
@@ -45884,15 +45884,15 @@
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">PL!E122/fx</f>
-        <v>4.54933275585715</v>
+        <v>4.54933275585716</v>
       </c>
       <c r="E14" s="23" t="n">
         <f aca="false">PL!F122/fx</f>
-        <v>4.82306460304253</v>
+        <v>4.82306460304254</v>
       </c>
       <c r="F14" s="23" t="n">
         <f aca="false">PL!G122/fx</f>
-        <v>5.90125011471097</v>
+        <v>5.90125011471098</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45928,7 +45928,7 @@
       </c>
       <c r="C16" s="21" t="n">
         <f aca="false">PL!D133</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="D16" s="21" t="n">
         <f aca="false">PL!E133</f>
@@ -46036,7 +46036,7 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">PL!D116*PL!D118-PL!D127/fx</f>
-        <v>8.22592366787716</v>
+        <v>8.22592366787715</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">PL!E116*PL!E118-PL!E127/fx</f>
@@ -46287,7 +46287,7 @@
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">G86</f>
-        <v>1.36894330525409</v>
+        <v>1.3689433052541</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46836,7 +46836,7 @@
       </c>
       <c r="J27" s="26" t="n">
         <f aca="false">J147</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46937,7 +46937,7 @@
       </c>
       <c r="F32" s="17" t="n">
         <f aca="false">F176</f>
-        <v>-0.0377720329791973</v>
+        <v>-0.0377720329791965</v>
       </c>
       <c r="G32" s="17" t="n">
         <f aca="false">G176</f>
@@ -46977,11 +46977,11 @@
       </c>
       <c r="F33" s="22" t="n">
         <f aca="false">F173</f>
-        <v>86.6738468002</v>
+        <v>86.6738468002001</v>
       </c>
       <c r="G33" s="22" t="n">
         <f aca="false">G173</f>
-        <v>97.0591925416626</v>
+        <v>97.0591925416627</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47029,11 +47029,11 @@
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">F178</f>
-        <v>0.766259342158442</v>
+        <v>0.766259342158443</v>
       </c>
       <c r="G35" s="17" t="n">
         <f aca="false">G178</f>
-        <v>0.718113348391436</v>
+        <v>0.718113348391437</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47121,7 +47121,7 @@
       </c>
       <c r="H38" s="24" t="n">
         <f aca="false">H190</f>
-        <v>23.9266262221066</v>
+        <v>23.9266262221067</v>
       </c>
       <c r="I38" s="24" t="n">
         <f aca="false">I190</f>
@@ -47129,7 +47129,7 @@
       </c>
       <c r="J38" s="24" t="n">
         <f aca="false">J190</f>
-        <v>21.7913056521721</v>
+        <v>21.7913056521722</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47161,7 +47161,7 @@
       </c>
       <c r="H39" s="25" t="n">
         <f aca="false">H195</f>
-        <v>0.146858287179497</v>
+        <v>0.146858287179498</v>
       </c>
       <c r="I39" s="25" t="n">
         <f aca="false">I195</f>
@@ -47193,19 +47193,19 @@
       </c>
       <c r="F40" s="18" t="n">
         <f aca="false">F193</f>
-        <v>45.3082538054553</v>
+        <v>45.3082538054554</v>
       </c>
       <c r="G40" s="18" t="n">
         <f aca="false">G193</f>
-        <v>45.5423835990202</v>
+        <v>45.5423835990203</v>
       </c>
       <c r="H40" s="26" t="n">
         <f aca="false">H193</f>
-        <v>44.7547425416571</v>
+        <v>44.7547425416572</v>
       </c>
       <c r="I40" s="26" t="n">
         <f aca="false">I193</f>
-        <v>42.8628861791176</v>
+        <v>42.8628861791177</v>
       </c>
       <c r="J40" s="26" t="n">
         <f aca="false">J193</f>
@@ -47233,19 +47233,19 @@
       </c>
       <c r="G41" s="17" t="n">
         <f aca="false">G194</f>
-        <v>0.00516748658136779</v>
+        <v>0.00516748658136801</v>
       </c>
       <c r="H41" s="25" t="n">
         <f aca="false">H194</f>
-        <v>-0.0172946823402544</v>
+        <v>-0.0172946823402542</v>
       </c>
       <c r="I41" s="25" t="n">
         <f aca="false">I194</f>
-        <v>-0.0422716399447189</v>
+        <v>-0.0422716399447191</v>
       </c>
       <c r="J41" s="25" t="n">
         <f aca="false">J194</f>
-        <v>-0.0677837014470677</v>
+        <v>-0.0677837014470676</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47343,7 +47343,7 @@
       </c>
       <c r="D63" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -47511,7 +47511,7 @@
       </c>
       <c r="D70" s="23" t="n">
         <f aca="false">D65*D69/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E70" s="23" t="n">
         <f aca="false">E65*E69/1000</f>
@@ -47626,11 +47626,11 @@
       </c>
       <c r="E75" s="17" t="n">
         <f aca="false">$D$73*E74</f>
-        <v>0.186669386545694</v>
+        <v>0.186669386545695</v>
       </c>
       <c r="F75" s="17" t="n">
         <f aca="false">$D$73*F74</f>
-        <v>0.186669386545694</v>
+        <v>0.186669386545695</v>
       </c>
       <c r="G75" s="17" t="n">
         <f aca="false">$D$73*G74</f>
@@ -47658,7 +47658,7 @@
       </c>
       <c r="G76" s="22" t="n">
         <f aca="false">G71*G75*G72</f>
-        <v>275.736342447905</v>
+        <v>275.736342447906</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47921,7 +47921,7 @@
       </c>
       <c r="G86" s="17" t="n">
         <f aca="false">(G76+G80)/G79</f>
-        <v>1.36894330525409</v>
+        <v>1.3689433052541</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>523</v>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="D87" s="21" t="n">
         <f aca="false">D81/fx/D65*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E87" s="21" t="n">
         <f aca="false">E81/fx/E65*1000</f>
@@ -48470,7 +48470,7 @@
       </c>
       <c r="D109" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E109" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48638,7 +48638,7 @@
       </c>
       <c r="D116" s="23" t="n">
         <f aca="false">D111*D115/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E116" s="23" t="n">
         <f aca="false">E111*E115/1000</f>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="D133" s="21" t="n">
         <f aca="false">D127/fx/D111*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E133" s="21" t="n">
         <f aca="false">E127/fx/E111*1000</f>
@@ -49464,7 +49464,7 @@
       </c>
       <c r="J147" s="29" t="n">
         <f aca="false">J144/J146</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49597,7 +49597,7 @@
       </c>
       <c r="D155" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E155" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49765,7 +49765,7 @@
       </c>
       <c r="D162" s="23" t="n">
         <f aca="false">D157*D161/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E162" s="23" t="n">
         <f aca="false">E157*E161/1000</f>
@@ -49908,11 +49908,11 @@
       </c>
       <c r="F168" s="22" t="n">
         <f aca="false">F163*F167*F164</f>
-        <v>86.6738468002</v>
+        <v>86.6738468002001</v>
       </c>
       <c r="G168" s="22" t="n">
         <f aca="false">G163*G167*G164</f>
-        <v>97.0591925416626</v>
+        <v>97.0591925416627</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50020,11 +50020,11 @@
       </c>
       <c r="F173" s="22" t="n">
         <f aca="false">MIN(F168,F171-F172)</f>
-        <v>86.6738468002</v>
+        <v>86.6738468002001</v>
       </c>
       <c r="G173" s="22" t="n">
         <f aca="false">MIN(G168,G171-G172)</f>
-        <v>97.0591925416626</v>
+        <v>97.0591925416627</v>
       </c>
       <c r="K173" s="3" t="s">
         <v>517</v>
@@ -50107,7 +50107,7 @@
       </c>
       <c r="F176" s="17" t="n">
         <f aca="false">F175/E175-1</f>
-        <v>-0.0377720329791973</v>
+        <v>-0.0377720329791965</v>
       </c>
       <c r="G176" s="17" t="n">
         <f aca="false">G175/F175-1</f>
@@ -50151,7 +50151,7 @@
       </c>
       <c r="G177" s="17" t="n">
         <f aca="false">G173/G175</f>
-        <v>0.633521810078655</v>
+        <v>0.633521810078656</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50171,11 +50171,11 @@
       </c>
       <c r="F178" s="17" t="n">
         <f aca="false">(F168+F172)/F171</f>
-        <v>0.766259342158442</v>
+        <v>0.766259342158443</v>
       </c>
       <c r="G178" s="17" t="n">
         <f aca="false">(G168+G172)/G171</f>
-        <v>0.718113348391436</v>
+        <v>0.718113348391437</v>
       </c>
       <c r="K178" s="3" t="s">
         <v>523</v>
@@ -50190,7 +50190,7 @@
       </c>
       <c r="D179" s="21" t="n">
         <f aca="false">D173/fx/D157*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E179" s="21" t="n">
         <f aca="false">E173/fx/E157*1000</f>
@@ -50198,11 +50198,11 @@
       </c>
       <c r="F179" s="21" t="n">
         <f aca="false">F173/fx/F157*1000</f>
-        <v>85.5101348201401</v>
+        <v>85.5101348201402</v>
       </c>
       <c r="G179" s="21" t="n">
         <f aca="false">G173/fx/G157*1000</f>
-        <v>84.0586074977228</v>
+        <v>84.0586074977229</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50472,7 +50472,7 @@
       </c>
       <c r="H190" s="24" t="n">
         <f aca="false">H175*H195</f>
-        <v>23.9266262221066</v>
+        <v>23.9266262221067</v>
       </c>
       <c r="I190" s="24" t="n">
         <f aca="false">I175*I195</f>
@@ -50480,7 +50480,7 @@
       </c>
       <c r="J190" s="24" t="n">
         <f aca="false">J175*J195</f>
-        <v>21.7913056521721</v>
+        <v>21.7913056521722</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50575,19 +50575,19 @@
       </c>
       <c r="F193" s="23" t="n">
         <f aca="false">F190/F192</f>
-        <v>45.3082538054553</v>
+        <v>45.3082538054554</v>
       </c>
       <c r="G193" s="23" t="n">
         <f aca="false">G190/G192</f>
-        <v>45.5423835990202</v>
+        <v>45.5423835990203</v>
       </c>
       <c r="H193" s="29" t="n">
         <f aca="false">H190/H192</f>
-        <v>44.7547425416571</v>
+        <v>44.7547425416572</v>
       </c>
       <c r="I193" s="29" t="n">
         <f aca="false">I190/I192</f>
-        <v>42.8628861791176</v>
+        <v>42.8628861791177</v>
       </c>
       <c r="J193" s="29" t="n">
         <f aca="false">J190/J192</f>
@@ -50615,19 +50615,19 @@
       </c>
       <c r="G194" s="17" t="n">
         <f aca="false">G193/F193-1</f>
-        <v>0.00516748658136779</v>
+        <v>0.00516748658136801</v>
       </c>
       <c r="H194" s="25" t="n">
         <f aca="false">H193/G193-1</f>
-        <v>-0.0172946823402544</v>
+        <v>-0.0172946823402542</v>
       </c>
       <c r="I194" s="25" t="n">
         <f aca="false">I193/H193-1</f>
-        <v>-0.0422716399447189</v>
+        <v>-0.0422716399447191</v>
       </c>
       <c r="J194" s="25" t="n">
         <f aca="false">J193/I193-1</f>
-        <v>-0.0677837014470677</v>
+        <v>-0.0677837014470676</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50659,7 +50659,7 @@
       </c>
       <c r="H195" s="25" t="n">
         <f aca="false">$G195+(fade_mC-$G195)*1/3</f>
-        <v>0.146858287179497</v>
+        <v>0.146858287179498</v>
       </c>
       <c r="I195" s="25" t="n">
         <f aca="false">$G195+(fade_mC-$G195)*2/3</f>
@@ -50769,7 +50769,7 @@
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">PL!F40</f>
-        <v>45.3082538054553</v>
+        <v>45.3082538054554</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50786,7 +50786,7 @@
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">PL!G40</f>
-        <v>45.5423835990202</v>
+        <v>45.5423835990203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50803,7 +50803,7 @@
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">PL!H40</f>
-        <v>44.7547425416571</v>
+        <v>44.7547425416572</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50820,7 +50820,7 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">PL!I40</f>
-        <v>42.8628861791176</v>
+        <v>42.8628861791177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50833,7 +50833,7 @@
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">PL!J27</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">PL!J40</f>
@@ -50905,7 +50905,7 @@
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">D10*(1-$B$15)</f>
-        <v>39.2729261803183</v>
+        <v>39.2729261803184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50973,7 +50973,7 @@
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(D16:D21,1/(1+tp_r)^{1;2;3;4;5;6})+D21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>508.19581594466</v>
+        <v>508.195815944661</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>557</v>
@@ -50993,7 +50993,7 @@
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">D22*(1+tp_r)</f>
-        <v>559.015397539126</v>
+        <v>559.015397539127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51243,7 +51243,7 @@
       </c>
       <c r="B44" s="17" t="n">
         <f aca="false">B41/px-1</f>
-        <v>0.1940448648212</v>
+        <v>0.194044864821201</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51742,7 +51742,7 @@
       </c>
       <c r="D79" s="20" t="n">
         <f aca="false">px*A79/PL!F40</f>
-        <v>29.7771352167529</v>
+        <v>29.7771352167528</v>
       </c>
       <c r="E79" s="20" t="n">
         <f aca="false">pe_mid</f>
@@ -51763,7 +51763,7 @@
       </c>
       <c r="D80" s="20" t="n">
         <f aca="false">px*A80/PL!F40</f>
-        <v>36.9138039877102</v>
+        <v>36.9138039877101</v>
       </c>
       <c r="E80" s="20" t="n">
         <f aca="false">pe_mid</f>
@@ -51784,7 +51784,7 @@
       </c>
       <c r="D81" s="20" t="n">
         <f aca="false">px*A81/PL!F40</f>
-        <v>49.2184053169469</v>
+        <v>49.2184053169468</v>
       </c>
       <c r="E81" s="20" t="n">
         <f aca="false">pe_mid</f>
@@ -52577,11 +52577,11 @@
       </c>
       <c r="G13" s="23" t="n">
         <f aca="false">PL!F193</f>
-        <v>45.3082538054553</v>
+        <v>45.3082538054554</v>
       </c>
       <c r="H13" s="17" t="n">
         <f aca="false">G13/B13-1</f>
-        <v>-0.524821669580962</v>
+        <v>-0.524821669580961</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>703</v>
@@ -52613,7 +52613,7 @@
       </c>
       <c r="G14" s="23" t="n">
         <f aca="false">PL!F193</f>
-        <v>45.3082538054553</v>
+        <v>45.3082538054554</v>
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">G14/B14-1</f>
@@ -52872,27 +52872,27 @@
       </c>
       <c r="C22" s="21" t="n">
         <f aca="false">PL!D87</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">C22/B22-1</f>
-        <v>-0.34053041323635</v>
+        <v>-0.340530413236349</v>
       </c>
       <c r="E22" s="21" t="n">
         <f aca="false">PL!D133</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">E22/B22-1</f>
-        <v>-0.34053041323635</v>
+        <v>-0.340530413236349</v>
       </c>
       <c r="G22" s="21" t="n">
         <f aca="false">PL!D179</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="H22" s="17" t="n">
         <f aca="false">G22/B22-1</f>
-        <v>-0.34053041323635</v>
+        <v>-0.340530413236349</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>731</v>
@@ -52911,27 +52911,27 @@
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">PL!D87</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="D23" s="17" t="n">
         <f aca="false">C23/B23-1</f>
-        <v>-0.543050764545568</v>
+        <v>-0.543050764545567</v>
       </c>
       <c r="E23" s="21" t="n">
         <f aca="false">PL!D133</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="F23" s="17" t="n">
         <f aca="false">E23/B23-1</f>
-        <v>-0.543050764545568</v>
+        <v>-0.543050764545567</v>
       </c>
       <c r="G23" s="21" t="n">
         <f aca="false">PL!D179</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="H23" s="17" t="n">
         <f aca="false">G23/B23-1</f>
-        <v>-0.543050764545568</v>
+        <v>-0.543050764545567</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>728</v>
@@ -53032,7 +53032,7 @@
       </c>
       <c r="D26" s="17" t="n">
         <f aca="false">C26-B26</f>
-        <v>-0.0746897693910075</v>
+        <v>-0.0746897693910072</v>
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">PL!D119</f>
@@ -53040,7 +53040,7 @@
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">E26-B26</f>
-        <v>-0.0746897693910075</v>
+        <v>-0.0746897693910072</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">PL!D165</f>
@@ -53048,7 +53048,7 @@
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">G26-B26</f>
-        <v>-0.0746897693910075</v>
+        <v>-0.0746897693910072</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>731</v>
@@ -53099,7 +53099,7 @@
       </c>
       <c r="G29" s="17" t="n">
         <f aca="false">PL!F178</f>
-        <v>0.766259342158442</v>
+        <v>0.766259342158443</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>56</v>
@@ -53392,11 +53392,11 @@
       </c>
       <c r="K5" s="18" t="n">
         <f aca="false">F91</f>
-        <v>74.6026961722779</v>
+        <v>74.602696172278</v>
       </c>
       <c r="L5" s="17" t="n">
         <f aca="false">K5/K$4-1</f>
-        <v>-0.0255855892208107</v>
+        <v>-0.0255855892208097</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53584,11 +53584,11 @@
       </c>
       <c r="K9" s="18" t="n">
         <f aca="false">F275</f>
-        <v>68.3517872509692</v>
+        <v>68.3517872509693</v>
       </c>
       <c r="L9" s="17" t="n">
         <f aca="false">K9/K$4-1</f>
-        <v>-0.10723110668744</v>
+        <v>-0.107231106687439</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53820,15 +53820,15 @@
       </c>
       <c r="J14" s="17" t="n">
         <f aca="false">F496</f>
-        <v>0.367849633361579</v>
+        <v>0.36784963336158</v>
       </c>
       <c r="K14" s="18" t="n">
         <f aca="false">F505</f>
-        <v>83.1885445411441</v>
+        <v>83.1885445411442</v>
       </c>
       <c r="L14" s="17" t="n">
         <f aca="false">K14/K$4-1</f>
-        <v>0.0865574673795628</v>
+        <v>0.0865574673795642</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53972,7 +53972,7 @@
       </c>
       <c r="L17" s="17" t="n">
         <f aca="false">K17/K$4-1</f>
-        <v>-0.0975036497210766</v>
+        <v>-0.0975036497210761</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54437,7 +54437,7 @@
       </c>
       <c r="I27" s="22" t="n">
         <f aca="false">PL!F173</f>
-        <v>86.6738468002</v>
+        <v>86.6738468002001</v>
       </c>
       <c r="J27" s="17" t="n">
         <f aca="false">PL!F184</f>
@@ -54445,11 +54445,11 @@
       </c>
       <c r="K27" s="18" t="n">
         <f aca="false">PL!F193</f>
-        <v>45.3082538054553</v>
+        <v>45.3082538054554</v>
       </c>
       <c r="L27" s="17" t="n">
         <f aca="false">K27/K$4-1</f>
-        <v>-0.408211529871191</v>
+        <v>-0.40821152987119</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54527,7 +54527,7 @@
       </c>
       <c r="F34" s="17" t="n">
         <f aca="false">E34/E$33-1</f>
-        <v>-0.0647965007282135</v>
+        <v>-0.0647965007282133</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54551,7 +54551,7 @@
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">E35/E$33-1</f>
-        <v>0.0906928796894466</v>
+        <v>0.0906928796894468</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54575,7 +54575,7 @@
       </c>
       <c r="F36" s="17" t="n">
         <f aca="false">E36/E$33-1</f>
-        <v>0.0505791629291819</v>
+        <v>0.0505791629291821</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54599,7 +54599,7 @@
       </c>
       <c r="F37" s="17" t="n">
         <f aca="false">E37/E$33-1</f>
-        <v>-0.0348437759526576</v>
+        <v>-0.0348437759526575</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54641,7 +54641,7 @@
       </c>
       <c r="F39" s="17" t="n">
         <f aca="false">E39/E$33-1</f>
-        <v>-0.0202468826941181</v>
+        <v>-0.0202468826941179</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54698,7 +54698,7 @@
       </c>
       <c r="D53" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="D60" s="23" t="n">
         <f aca="false">D55*D59/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E60" s="23" t="n">
         <f aca="false">E55*E59/1000</f>
@@ -55208,7 +55208,7 @@
       </c>
       <c r="F74" s="17" t="n">
         <f aca="false">F73/E73-1</f>
-        <v>0.243076491854961</v>
+        <v>0.243076491854962</v>
       </c>
       <c r="G74" s="17" t="n">
         <f aca="false">G73/F73-1</f>
@@ -55252,7 +55252,7 @@
       </c>
       <c r="G75" s="17" t="n">
         <f aca="false">G71/G73</f>
-        <v>0.743425222844372</v>
+        <v>0.743425222844373</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55272,11 +55272,11 @@
       </c>
       <c r="F76" s="17" t="n">
         <f aca="false">(F66+F70)/F69</f>
-        <v>0.978003751052465</v>
+        <v>0.978003751052466</v>
       </c>
       <c r="G76" s="17" t="n">
         <f aca="false">(G66+G70)/G69</f>
-        <v>0.960244860648688</v>
+        <v>0.960244860648689</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>523</v>
@@ -55291,7 +55291,7 @@
       </c>
       <c r="D77" s="21" t="n">
         <f aca="false">D71/fx/D55*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E77" s="21" t="n">
         <f aca="false">E71/fx/E55*1000</f>
@@ -55303,7 +55303,7 @@
       </c>
       <c r="G77" s="21" t="n">
         <f aca="false">G71/fx/G55*1000</f>
-        <v>99.4544935529256</v>
+        <v>99.4544935529257</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55374,7 +55374,7 @@
       </c>
       <c r="F81" s="22" t="n">
         <f aca="false">F71*F80+F70*$D$79</f>
-        <v>69.4146800676271</v>
+        <v>69.4146800676272</v>
       </c>
       <c r="G81" s="22" t="n">
         <f aca="false">G71*G80+G70*$D$79</f>
@@ -55490,7 +55490,7 @@
       </c>
       <c r="G85" s="22" t="n">
         <f aca="false">G81-G84</f>
-        <v>64.7134297504206</v>
+        <v>64.7134297504207</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55569,11 +55569,11 @@
       </c>
       <c r="G88" s="22" t="n">
         <f aca="false">(G85+G87)*nir_f</f>
-        <v>44.3286993790381</v>
+        <v>44.3286993790382</v>
       </c>
       <c r="H88" s="24" t="n">
         <f aca="false">H73*H93</f>
-        <v>46.335586942777</v>
+        <v>46.3355869427771</v>
       </c>
       <c r="I88" s="24" t="n">
         <f aca="false">I73*I93</f>
@@ -55581,7 +55581,7 @@
       </c>
       <c r="J88" s="24" t="n">
         <f aca="false">J73*J93</f>
-        <v>45.0336417052813</v>
+        <v>45.0336417052814</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55676,23 +55676,23 @@
       </c>
       <c r="F91" s="23" t="n">
         <f aca="false">F88/F90</f>
-        <v>74.6026961722779</v>
+        <v>74.602696172278</v>
       </c>
       <c r="G91" s="23" t="n">
         <f aca="false">G88/G90</f>
-        <v>83.7459784172656</v>
+        <v>83.7459784172657</v>
       </c>
       <c r="H91" s="29" t="n">
         <f aca="false">H88/H90</f>
-        <v>86.6706925117826</v>
+        <v>86.6706925117827</v>
       </c>
       <c r="I91" s="29" t="n">
         <f aca="false">I88/I90</f>
-        <v>86.3181322715959</v>
+        <v>86.318132271596</v>
       </c>
       <c r="J91" s="29" t="n">
         <f aca="false">J88/J90</f>
-        <v>82.5756343373224</v>
+        <v>82.5756343373225</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55712,7 +55712,7 @@
       </c>
       <c r="F92" s="17" t="n">
         <f aca="false">F91/E91-1</f>
-        <v>0.240256473371662</v>
+        <v>0.240256473371663</v>
       </c>
       <c r="G92" s="17" t="n">
         <f aca="false">G91/F91-1</f>
@@ -55720,7 +55720,7 @@
       </c>
       <c r="H92" s="25" t="n">
         <f aca="false">H91/G91-1</f>
-        <v>0.034923636332058</v>
+        <v>0.0349236363320582</v>
       </c>
       <c r="I92" s="25" t="n">
         <f aca="false">I91/H91-1</f>
@@ -55728,7 +55728,7 @@
       </c>
       <c r="J92" s="25" t="n">
         <f aca="false">J91/I91-1</f>
-        <v>-0.0433570309711746</v>
+        <v>-0.0433570309711748</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55825,7 +55825,7 @@
       </c>
       <c r="D99" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E99" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55993,7 +55993,7 @@
       </c>
       <c r="D106" s="23" t="n">
         <f aca="false">D101*D105/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E106" s="23" t="n">
         <f aca="false">E101*E105/1000</f>
@@ -56140,7 +56140,7 @@
       </c>
       <c r="G112" s="22" t="n">
         <f aca="false">G107*G111*G108</f>
-        <v>214.995360733951</v>
+        <v>214.995360733952</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56418,7 +56418,7 @@
       </c>
       <c r="D123" s="21" t="n">
         <f aca="false">D117/fx/D101*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E123" s="21" t="n">
         <f aca="false">E117/fx/E101*1000</f>
@@ -56819,7 +56819,7 @@
       </c>
       <c r="J137" s="29" t="n">
         <f aca="false">J134/J136</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56952,7 +56952,7 @@
       </c>
       <c r="D145" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E145" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57120,7 +57120,7 @@
       </c>
       <c r="D152" s="23" t="n">
         <f aca="false">D147*D151/1000</f>
-        <v>9.35981521682557</v>
+        <v>9.35981521682555</v>
       </c>
       <c r="E152" s="23" t="n">
         <f aca="false">E147*E151/1000</f>
@@ -57263,11 +57263,11 @@
       </c>
       <c r="F158" s="22" t="n">
         <f aca="false">F153*F157*F154</f>
-        <v>146.831037873378</v>
+        <v>146.831037873379</v>
       </c>
       <c r="G158" s="22" t="n">
         <f aca="false">G153*G157*G154</f>
-        <v>178.405367622446</v>
+        <v>178.405367622447</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57545,7 +57545,7 @@
       </c>
       <c r="D169" s="21" t="n">
         <f aca="false">D163/fx/D147*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E169" s="21" t="n">
         <f aca="false">E163/fx/E147*1000</f>
@@ -57946,7 +57946,7 @@
       </c>
       <c r="J183" s="29" t="n">
         <f aca="false">J180/J182</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58079,7 +58079,7 @@
       </c>
       <c r="D191" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E191" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58247,7 +58247,7 @@
       </c>
       <c r="D198" s="23" t="n">
         <f aca="false">D193*D197/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E198" s="23" t="n">
         <f aca="false">E193*E197/1000</f>
@@ -58657,7 +58657,7 @@
       </c>
       <c r="G214" s="17" t="n">
         <f aca="false">(G204+G208)/G207</f>
-        <v>1.11571646791475</v>
+        <v>1.11571646791476</v>
       </c>
       <c r="K214" s="3" t="s">
         <v>523</v>
@@ -58672,7 +58672,7 @@
       </c>
       <c r="D215" s="21" t="n">
         <f aca="false">D209/fx/D193*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E215" s="21" t="n">
         <f aca="false">E209/fx/E193*1000</f>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="J229" s="29" t="n">
         <f aca="false">J226/J228</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59206,7 +59206,7 @@
       </c>
       <c r="D237" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E237" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59374,7 +59374,7 @@
       </c>
       <c r="D244" s="23" t="n">
         <f aca="false">D239*D243/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E244" s="23" t="n">
         <f aca="false">E239*E243/1000</f>
@@ -59716,11 +59716,11 @@
       </c>
       <c r="F258" s="17" t="n">
         <f aca="false">F257/E257-1</f>
-        <v>0.153860464232662</v>
+        <v>0.153860464232663</v>
       </c>
       <c r="G258" s="17" t="n">
         <f aca="false">G257/F257-1</f>
-        <v>0.151199222398062</v>
+        <v>0.151199222398063</v>
       </c>
       <c r="H258" s="25" t="n">
         <f aca="false">$G258+(fade_gB-$G258)*1/3</f>
@@ -59780,7 +59780,7 @@
       </c>
       <c r="F260" s="17" t="n">
         <f aca="false">(F250+F254)/F253</f>
-        <v>0.907812085261725</v>
+        <v>0.907812085261726</v>
       </c>
       <c r="G260" s="17" t="n">
         <f aca="false">(G250+G254)/G253</f>
@@ -59799,7 +59799,7 @@
       </c>
       <c r="D261" s="21" t="n">
         <f aca="false">D255/fx/D239*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E261" s="21" t="n">
         <f aca="false">E255/fx/E239*1000</f>
@@ -59807,11 +59807,11 @@
       </c>
       <c r="F261" s="21" t="n">
         <f aca="false">F255/fx/F239*1000</f>
-        <v>90.1574247560173</v>
+        <v>90.1574247560174</v>
       </c>
       <c r="G261" s="21" t="n">
         <f aca="false">G255/fx/G239*1000</f>
-        <v>89.7898761907493</v>
+        <v>89.7898761907494</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59882,11 +59882,11 @@
       </c>
       <c r="F265" s="22" t="n">
         <f aca="false">F255*F264+F254*$D$263</f>
-        <v>64.0558551505947</v>
+        <v>64.0558551505948</v>
       </c>
       <c r="G265" s="22" t="n">
         <f aca="false">G255*G264+G254*$D$263</f>
-        <v>72.1962595202713</v>
+        <v>72.1962595202714</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59994,11 +59994,11 @@
       </c>
       <c r="F269" s="22" t="n">
         <f aca="false">F265-F268</f>
-        <v>52.2948543667273</v>
+        <v>52.2948543667274</v>
       </c>
       <c r="G269" s="22" t="n">
         <f aca="false">G265-G268</f>
-        <v>59.3683062325177</v>
+        <v>59.3683062325178</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60073,11 +60073,11 @@
       </c>
       <c r="F272" s="22" t="n">
         <f aca="false">(F269+F271)*nir_f</f>
-        <v>35.8219752412082</v>
+        <v>35.8219752412083</v>
       </c>
       <c r="G272" s="22" t="n">
         <f aca="false">(G269+G271)*nir_f</f>
-        <v>40.6672897692746</v>
+        <v>40.6672897692747</v>
       </c>
       <c r="H272" s="24" t="n">
         <f aca="false">H257*H277</f>
@@ -60085,11 +60085,11 @@
       </c>
       <c r="I272" s="24" t="n">
         <f aca="false">I257*I277</f>
-        <v>43.0348052373331</v>
+        <v>43.0348052373332</v>
       </c>
       <c r="J272" s="24" t="n">
         <f aca="false">J257*J277</f>
-        <v>41.7580124881924</v>
+        <v>41.7580124881925</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60184,23 +60184,23 @@
       </c>
       <c r="F275" s="23" t="n">
         <f aca="false">F272/F274</f>
-        <v>68.3517872509692</v>
+        <v>68.3517872509693</v>
       </c>
       <c r="G275" s="23" t="n">
         <f aca="false">G272/G274</f>
-        <v>76.828826900273</v>
+        <v>76.8288269002731</v>
       </c>
       <c r="H275" s="29" t="n">
         <f aca="false">H272/H274</f>
-        <v>79.7434480946746</v>
+        <v>79.7434480946747</v>
       </c>
       <c r="I275" s="29" t="n">
         <f aca="false">I272/I274</f>
-        <v>79.6995860995525</v>
+        <v>79.6995860995526</v>
       </c>
       <c r="J275" s="29" t="n">
         <f aca="false">J272/J274</f>
-        <v>76.5692988465095</v>
+        <v>76.5692988465096</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60220,7 +60220,7 @@
       </c>
       <c r="F276" s="17" t="n">
         <f aca="false">F275/E275-1</f>
-        <v>0.136336231183543</v>
+        <v>0.136336231183545</v>
       </c>
       <c r="G276" s="17" t="n">
         <f aca="false">G275/F275-1</f>
@@ -60232,11 +60232,11 @@
       </c>
       <c r="I276" s="25" t="n">
         <f aca="false">I275/H275-1</f>
-        <v>-0.000550038857988877</v>
+        <v>-0.000550038857988655</v>
       </c>
       <c r="J276" s="25" t="n">
         <f aca="false">J275/I275-1</f>
-        <v>-0.0392760791647402</v>
+        <v>-0.0392760791647405</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60272,7 +60272,7 @@
       </c>
       <c r="I277" s="25" t="n">
         <f aca="false">$G277+(fade_mB-$G277)*2/3</f>
-        <v>0.176643237883421</v>
+        <v>0.176643237883422</v>
       </c>
       <c r="J277" s="25" t="n">
         <f aca="false">$G277+(fade_mB-$G277)*3/3</f>
@@ -60333,7 +60333,7 @@
       </c>
       <c r="D283" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E283" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -60501,7 +60501,7 @@
       </c>
       <c r="D290" s="23" t="n">
         <f aca="false">D285*D289/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E290" s="23" t="n">
         <f aca="false">E285*E289/1000</f>
@@ -60616,11 +60616,11 @@
       </c>
       <c r="E295" s="17" t="n">
         <f aca="false">$D$293*E294</f>
-        <v>0.186669386545694</v>
+        <v>0.186669386545695</v>
       </c>
       <c r="F295" s="17" t="n">
         <f aca="false">$D$293*F294</f>
-        <v>0.186669386545694</v>
+        <v>0.186669386545695</v>
       </c>
       <c r="G295" s="17" t="n">
         <f aca="false">$D$293*G294</f>
@@ -60648,7 +60648,7 @@
       </c>
       <c r="G296" s="22" t="n">
         <f aca="false">G291*G295*G292</f>
-        <v>220.313337615876</v>
+        <v>220.313337615877</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60903,7 +60903,7 @@
       </c>
       <c r="E306" s="17" t="n">
         <f aca="false">(E296+E300)/E299</f>
-        <v>1.37494913038739</v>
+        <v>1.3749491303874</v>
       </c>
       <c r="F306" s="17" t="n">
         <f aca="false">(F296+F300)/F299</f>
@@ -60926,7 +60926,7 @@
       </c>
       <c r="D307" s="21" t="n">
         <f aca="false">D301/fx/D285*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E307" s="21" t="n">
         <f aca="false">E301/fx/E285*1000</f>
@@ -61327,7 +61327,7 @@
       </c>
       <c r="J321" s="29" t="n">
         <f aca="false">J318/J320</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61460,7 +61460,7 @@
       </c>
       <c r="D329" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E329" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61628,7 +61628,7 @@
       </c>
       <c r="D336" s="23" t="n">
         <f aca="false">D331*D335/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E336" s="23" t="n">
         <f aca="false">E331*E335/1000</f>
@@ -62034,7 +62034,7 @@
       </c>
       <c r="F352" s="17" t="n">
         <f aca="false">(F342+F346)/F345</f>
-        <v>1.09031844724542</v>
+        <v>1.09031844724543</v>
       </c>
       <c r="G352" s="17" t="n">
         <f aca="false">(G342+G346)/G345</f>
@@ -62053,7 +62053,7 @@
       </c>
       <c r="D353" s="21" t="n">
         <f aca="false">D347/fx/D331*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E353" s="21" t="n">
         <f aca="false">E347/fx/E331*1000</f>
@@ -62454,7 +62454,7 @@
       </c>
       <c r="J367" s="29" t="n">
         <f aca="false">J364/J366</f>
-        <v>80.9522404126301</v>
+        <v>80.9522404126302</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62482,7 +62482,7 @@
       </c>
       <c r="H368" s="25" t="n">
         <f aca="false">H367/G367-1</f>
-        <v>0.0767557380642021</v>
+        <v>0.0767557380642023</v>
       </c>
       <c r="I368" s="25" t="n">
         <f aca="false">I367/H367-1</f>
@@ -62490,7 +62490,7 @@
       </c>
       <c r="J368" s="25" t="n">
         <f aca="false">J367/I367-1</f>
-        <v>-0.000583516499514158</v>
+        <v>-0.000583516499513714</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62587,7 +62587,7 @@
       </c>
       <c r="D375" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E375" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62755,7 +62755,7 @@
       </c>
       <c r="D382" s="23" t="n">
         <f aca="false">D377*D381/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E382" s="23" t="n">
         <f aca="false">E377*E381/1000</f>
@@ -62898,7 +62898,7 @@
       </c>
       <c r="F388" s="22" t="n">
         <f aca="false">F383*F387*F384</f>
-        <v>162.293637776606</v>
+        <v>162.293637776607</v>
       </c>
       <c r="G388" s="22" t="n">
         <f aca="false">G383*G387*G384</f>
@@ -63180,7 +63180,7 @@
       </c>
       <c r="D399" s="21" t="n">
         <f aca="false">D393/fx/D377*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E399" s="21" t="n">
         <f aca="false">E393/fx/E377*1000</f>
@@ -63581,7 +63581,7 @@
       </c>
       <c r="J413" s="29" t="n">
         <f aca="false">J410/J412</f>
-        <v>94.4104931122724</v>
+        <v>94.4104931122725</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63609,7 +63609,7 @@
       </c>
       <c r="H414" s="25" t="n">
         <f aca="false">H413/G413-1</f>
-        <v>0.0253072418464366</v>
+        <v>0.0253072418464368</v>
       </c>
       <c r="I414" s="25" t="n">
         <f aca="false">I413/H413-1</f>
@@ -63617,7 +63617,7 @@
       </c>
       <c r="J414" s="25" t="n">
         <f aca="false">J413/I413-1</f>
-        <v>-0.0831686887265656</v>
+        <v>-0.0831686887265652</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63714,7 +63714,7 @@
       </c>
       <c r="D421" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E421" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -63882,7 +63882,7 @@
       </c>
       <c r="D428" s="23" t="n">
         <f aca="false">D423*D427/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E428" s="23" t="n">
         <f aca="false">E423*E427/1000</f>
@@ -64284,7 +64284,7 @@
       </c>
       <c r="E444" s="17" t="n">
         <f aca="false">(E434+E438)/E437</f>
-        <v>1.44860614956729</v>
+        <v>1.4486061495673</v>
       </c>
       <c r="F444" s="17" t="n">
         <f aca="false">(F434+F438)/F437</f>
@@ -64307,7 +64307,7 @@
       </c>
       <c r="D445" s="21" t="n">
         <f aca="false">D439/fx/D423*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E445" s="21" t="n">
         <f aca="false">E439/fx/E423*1000</f>
@@ -64708,7 +64708,7 @@
       </c>
       <c r="J459" s="29" t="n">
         <f aca="false">J456/J458</f>
-        <v>70.9735211138462</v>
+        <v>70.9735211138463</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64736,7 +64736,7 @@
       </c>
       <c r="H460" s="25" t="n">
         <f aca="false">H459/G459-1</f>
-        <v>0.0410916982435283</v>
+        <v>0.0410916982435285</v>
       </c>
       <c r="I460" s="25" t="n">
         <f aca="false">I459/H459-1</f>
@@ -64744,7 +64744,7 @@
       </c>
       <c r="J460" s="25" t="n">
         <f aca="false">J459/I459-1</f>
-        <v>-0.0351988456977964</v>
+        <v>-0.0351988456977962</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64841,7 +64841,7 @@
       </c>
       <c r="D467" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E467" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -65009,7 +65009,7 @@
       </c>
       <c r="D474" s="23" t="n">
         <f aca="false">D469*D473/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E474" s="23" t="n">
         <f aca="false">E469*E473/1000</f>
@@ -65320,15 +65320,15 @@
       </c>
       <c r="H487" s="24" t="n">
         <f aca="false">G487*(1+H488)</f>
-        <v>276.51314181298</v>
+        <v>276.513141812981</v>
       </c>
       <c r="I487" s="24" t="n">
         <f aca="false">H487*(1+I488)</f>
-        <v>299.835216686253</v>
+        <v>299.835216686254</v>
       </c>
       <c r="J487" s="24" t="n">
         <f aca="false">I487*(1+J488)</f>
-        <v>311.828625353703</v>
+        <v>311.828625353704</v>
       </c>
       <c r="K487" s="7" t="s">
         <v>519</v>
@@ -65351,11 +65351,11 @@
       </c>
       <c r="F488" s="17" t="n">
         <f aca="false">F487/E487-1</f>
-        <v>0.23834441044482</v>
+        <v>0.238344410444821</v>
       </c>
       <c r="G488" s="17" t="n">
         <f aca="false">G487/F487-1</f>
-        <v>0.1730303773668</v>
+        <v>0.173030377366801</v>
       </c>
       <c r="H488" s="25" t="n">
         <f aca="false">$G488+(fade_gB-$G488)*1/3</f>
@@ -65391,7 +65391,7 @@
       </c>
       <c r="F489" s="17" t="n">
         <f aca="false">F485/F487</f>
-        <v>0.738992500606225</v>
+        <v>0.738992500606226</v>
       </c>
       <c r="G489" s="17" t="n">
         <f aca="false">G485/G487</f>
@@ -65415,11 +65415,11 @@
       </c>
       <c r="F490" s="17" t="n">
         <f aca="false">(F480+F484)/F483</f>
-        <v>0.950060444359488</v>
+        <v>0.950060444359489</v>
       </c>
       <c r="G490" s="17" t="n">
         <f aca="false">(G480+G484)/G483</f>
-        <v>0.950975850143473</v>
+        <v>0.950975850143474</v>
       </c>
       <c r="K490" s="3" t="s">
         <v>523</v>
@@ -65434,7 +65434,7 @@
       </c>
       <c r="D491" s="21" t="n">
         <f aca="false">D485/fx/D469*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E491" s="21" t="n">
         <f aca="false">E485/fx/E469*1000</f>
@@ -65446,7 +65446,7 @@
       </c>
       <c r="G491" s="21" t="n">
         <f aca="false">G485/fx/G469*1000</f>
-        <v>115.444126530963</v>
+        <v>115.444126530964</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65517,11 +65517,11 @@
       </c>
       <c r="F495" s="22" t="n">
         <f aca="false">F485*F494+F484*$D$493</f>
-        <v>76.8251388512003</v>
+        <v>76.8251388512004</v>
       </c>
       <c r="G495" s="22" t="n">
         <f aca="false">G485*G494+G484*$D$493</f>
-        <v>88.0648558084851</v>
+        <v>88.0648558084852</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65545,11 +65545,11 @@
       </c>
       <c r="F496" s="17" t="n">
         <f aca="false">F495/F487</f>
-        <v>0.367849633361579</v>
+        <v>0.36784963336158</v>
       </c>
       <c r="G496" s="17" t="n">
         <f aca="false">G495/G487</f>
-        <v>0.359468089134641</v>
+        <v>0.359468089134642</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65577,7 +65577,7 @@
       </c>
       <c r="G497" s="22" t="n">
         <f aca="false">F497*(1+MAX(0,phi*G488))</f>
-        <v>14.5471319146034</v>
+        <v>14.5471319146035</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65605,7 +65605,7 @@
       </c>
       <c r="G498" s="22" t="n">
         <f aca="false">G497+0*G487</f>
-        <v>14.5471319146034</v>
+        <v>14.5471319146035</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65629,11 +65629,11 @@
       </c>
       <c r="F499" s="22" t="n">
         <f aca="false">F495-F498</f>
-        <v>63.6462190196417</v>
+        <v>63.6462190196418</v>
       </c>
       <c r="G499" s="22" t="n">
         <f aca="false">G495-G498</f>
-        <v>73.5177238938816</v>
+        <v>73.5177238938817</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65712,7 +65712,7 @@
       </c>
       <c r="G502" s="22" t="n">
         <f aca="false">(G499+G501)*nir_f</f>
-        <v>50.3596408673089</v>
+        <v>50.359640867309</v>
       </c>
       <c r="H502" s="24" t="n">
         <f aca="false">H487*H507</f>
@@ -65720,7 +65720,7 @@
       </c>
       <c r="I502" s="24" t="n">
         <f aca="false">I487*I507</f>
-        <v>53.4886928856943</v>
+        <v>53.4886928856944</v>
       </c>
       <c r="J502" s="24" t="n">
         <f aca="false">J487*J507</f>
@@ -65819,23 +65819,23 @@
       </c>
       <c r="F505" s="23" t="n">
         <f aca="false">F502/F504</f>
-        <v>83.1885445411441</v>
+        <v>83.1885445411442</v>
       </c>
       <c r="G505" s="23" t="n">
         <f aca="false">G502/G504</f>
-        <v>95.1396602258356</v>
+        <v>95.1396602258357</v>
       </c>
       <c r="H505" s="29" t="n">
         <f aca="false">H502/H504</f>
-        <v>99.2940177248577</v>
+        <v>99.2940177248578</v>
       </c>
       <c r="I505" s="29" t="n">
         <f aca="false">I502/I504</f>
-        <v>99.059973909158</v>
+        <v>99.0599739091582</v>
       </c>
       <c r="J505" s="29" t="n">
         <f aca="false">J502/J504</f>
-        <v>94.2354884741128</v>
+        <v>94.235488474113</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65855,7 +65855,7 @@
       </c>
       <c r="F506" s="17" t="n">
         <f aca="false">F505/E505-1</f>
-        <v>0.230023426115795</v>
+        <v>0.230023426115796</v>
       </c>
       <c r="G506" s="17" t="n">
         <f aca="false">G505/F505-1</f>
@@ -65863,15 +65863,15 @@
       </c>
       <c r="H506" s="25" t="n">
         <f aca="false">H505/G505-1</f>
-        <v>0.0436658853853458</v>
+        <v>0.0436658853853456</v>
       </c>
       <c r="I506" s="25" t="n">
         <f aca="false">I505/H505-1</f>
-        <v>-0.00235707871493551</v>
+        <v>-0.00235707871493496</v>
       </c>
       <c r="J506" s="25" t="n">
         <f aca="false">J505/I505-1</f>
-        <v>-0.0487026721758418</v>
+        <v>-0.048702672175842</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65968,7 +65968,7 @@
       </c>
       <c r="D513" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E513" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -66136,7 +66136,7 @@
       </c>
       <c r="D520" s="23" t="n">
         <f aca="false">D515*D519/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E520" s="23" t="n">
         <f aca="false">E515*E519/1000</f>
@@ -66561,7 +66561,7 @@
       </c>
       <c r="D537" s="21" t="n">
         <f aca="false">D531/fx/D515*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E537" s="21" t="n">
         <f aca="false">E531/fx/E515*1000</f>
@@ -66958,11 +66958,11 @@
       </c>
       <c r="I551" s="29" t="n">
         <f aca="false">I548/I550</f>
-        <v>89.172194499915</v>
+        <v>89.1721944999151</v>
       </c>
       <c r="J551" s="29" t="n">
         <f aca="false">J548/J550</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66990,7 +66990,7 @@
       </c>
       <c r="H552" s="25" t="n">
         <f aca="false">H551/G551-1</f>
-        <v>0.0711576294420151</v>
+        <v>0.0711576294420153</v>
       </c>
       <c r="I552" s="25" t="n">
         <f aca="false">I551/H551-1</f>
@@ -67095,7 +67095,7 @@
       </c>
       <c r="D559" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E559" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -67263,7 +67263,7 @@
       </c>
       <c r="D566" s="23" t="n">
         <f aca="false">D561*D565/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E566" s="23" t="n">
         <f aca="false">E561*E565/1000</f>
@@ -67688,7 +67688,7 @@
       </c>
       <c r="D583" s="21" t="n">
         <f aca="false">D577/fx/D561*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E583" s="21" t="n">
         <f aca="false">E577/fx/E561*1000</f>
@@ -68089,7 +68089,7 @@
       </c>
       <c r="J597" s="29" t="n">
         <f aca="false">J594/J596</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="598" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68125,7 +68125,7 @@
       </c>
       <c r="J598" s="25" t="n">
         <f aca="false">J597/I597-1</f>
-        <v>-0.0591178344820086</v>
+        <v>-0.0591178344820085</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68222,7 +68222,7 @@
       </c>
       <c r="D605" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E605" s="23" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -68390,7 +68390,7 @@
       </c>
       <c r="D612" s="23" t="n">
         <f aca="false">D607*D611/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E612" s="23" t="n">
         <f aca="false">E607*E611/1000</f>
@@ -68709,7 +68709,7 @@
       </c>
       <c r="J625" s="24" t="n">
         <f aca="false">I625*(1+J626)</f>
-        <v>261.684406836981</v>
+        <v>261.684406836982</v>
       </c>
       <c r="K625" s="7" t="s">
         <v>519</v>
@@ -68732,7 +68732,7 @@
       </c>
       <c r="F626" s="17" t="n">
         <f aca="false">F625/E625-1</f>
-        <v>0.164489891252467</v>
+        <v>0.164489891252468</v>
       </c>
       <c r="G626" s="17" t="n">
         <f aca="false">G625/F625-1</f>
@@ -68776,7 +68776,7 @@
       </c>
       <c r="G627" s="17" t="n">
         <f aca="false">G623/G625</f>
-        <v>0.729046630194394</v>
+        <v>0.729046630194395</v>
       </c>
     </row>
     <row r="628" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68796,11 +68796,11 @@
       </c>
       <c r="F628" s="17" t="n">
         <f aca="false">(F618+F622)/F621</f>
-        <v>0.916174900876873</v>
+        <v>0.916174900876874</v>
       </c>
       <c r="G628" s="17" t="n">
         <f aca="false">(G618+G622)/G621</f>
-        <v>0.9092878649656</v>
+        <v>0.909287864965601</v>
       </c>
       <c r="K628" s="3" t="s">
         <v>523</v>
@@ -68815,7 +68815,7 @@
       </c>
       <c r="D629" s="21" t="n">
         <f aca="false">D623/fx/D607*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E629" s="21" t="n">
         <f aca="false">E623/fx/E607*1000</f>
@@ -68827,7 +68827,7 @@
       </c>
       <c r="G629" s="21" t="n">
         <f aca="false">G623/fx/G607*1000</f>
-        <v>115.444126530963</v>
+        <v>115.444126530964</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68898,11 +68898,11 @@
       </c>
       <c r="F633" s="22" t="n">
         <f aca="false">F623*F632+F622*$D$631</f>
-        <v>64.694319335625</v>
+        <v>64.6943193356251</v>
       </c>
       <c r="G633" s="22" t="n">
         <f aca="false">G623*G632+G622*$D$631</f>
-        <v>73.7831191490927</v>
+        <v>73.7831191490928</v>
       </c>
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69014,7 +69014,7 @@
       </c>
       <c r="G637" s="22" t="n">
         <f aca="false">G633-G636</f>
-        <v>60.7875007113602</v>
+        <v>60.7875007113603</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69097,15 +69097,15 @@
       </c>
       <c r="H640" s="24" t="n">
         <f aca="false">H625*H645</f>
-        <v>43.9521528980722</v>
+        <v>43.9521528980723</v>
       </c>
       <c r="I640" s="24" t="n">
         <f aca="false">I625*I645</f>
-        <v>44.5001545622165</v>
+        <v>44.5001545622166</v>
       </c>
       <c r="J640" s="24" t="n">
         <f aca="false">J625*J645</f>
-        <v>43.128216634554</v>
+        <v>43.1282166345541</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69204,19 +69204,19 @@
       </c>
       <c r="G643" s="23" t="n">
         <f aca="false">G640/G642</f>
-        <v>78.6654136899614</v>
+        <v>78.6654136899615</v>
       </c>
       <c r="H643" s="29" t="n">
         <f aca="false">H640/H642</f>
-        <v>82.2124803072876</v>
+        <v>82.2124803072878</v>
       </c>
       <c r="I643" s="29" t="n">
         <f aca="false">I640/I642</f>
-        <v>82.4133833164887</v>
+        <v>82.4133833164888</v>
       </c>
       <c r="J643" s="29" t="n">
         <f aca="false">J640/J642</f>
-        <v>79.081764467165</v>
+        <v>79.0817644671651</v>
       </c>
     </row>
     <row r="644" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69236,7 +69236,7 @@
       </c>
       <c r="F644" s="17" t="n">
         <f aca="false">F643/E643-1</f>
-        <v>0.148717556150124</v>
+        <v>0.148717556150125</v>
       </c>
       <c r="G644" s="17" t="n">
         <f aca="false">G643/F643-1</f>
@@ -69244,7 +69244,7 @@
       </c>
       <c r="H644" s="25" t="n">
         <f aca="false">H643/G643-1</f>
-        <v>0.045090548068635</v>
+        <v>0.0450905480686354</v>
       </c>
       <c r="I644" s="25" t="n">
         <f aca="false">I643/H643-1</f>
@@ -69349,7 +69349,7 @@
       </c>
       <c r="D651" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E651" s="23" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -69517,7 +69517,7 @@
       </c>
       <c r="D658" s="23" t="n">
         <f aca="false">D653*D657/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E658" s="23" t="n">
         <f aca="false">E653*E657/1000</f>
@@ -69664,7 +69664,7 @@
       </c>
       <c r="G664" s="22" t="n">
         <f aca="false">G659*G663*G660</f>
-        <v>226.608004404901</v>
+        <v>226.608004404902</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69919,11 +69919,11 @@
       </c>
       <c r="E674" s="17" t="n">
         <f aca="false">(E664+E668)/E667</f>
-        <v>1.48924731448143</v>
+        <v>1.48924731448144</v>
       </c>
       <c r="F674" s="17" t="n">
         <f aca="false">(F664+F668)/F667</f>
-        <v>1.23396189425249</v>
+        <v>1.2339618942525</v>
       </c>
       <c r="G674" s="17" t="n">
         <f aca="false">(G664+G668)/G667</f>
@@ -69942,7 +69942,7 @@
       </c>
       <c r="D675" s="21" t="n">
         <f aca="false">D669/fx/D653*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E675" s="21" t="n">
         <f aca="false">E669/fx/E653*1000</f>
@@ -70343,7 +70343,7 @@
       </c>
       <c r="J689" s="29" t="n">
         <f aca="false">J686/J688</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70476,7 +70476,7 @@
       </c>
       <c r="D697" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E697" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -70644,7 +70644,7 @@
       </c>
       <c r="D704" s="23" t="n">
         <f aca="false">D699*D703/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E704" s="23" t="n">
         <f aca="false">E699*E703/1000</f>
@@ -71069,7 +71069,7 @@
       </c>
       <c r="D721" s="21" t="n">
         <f aca="false">D715/fx/D699*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E721" s="21" t="n">
         <f aca="false">E715/fx/E699*1000</f>
@@ -71470,7 +71470,7 @@
       </c>
       <c r="J735" s="29" t="n">
         <f aca="false">J732/J734</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71603,7 +71603,7 @@
       </c>
       <c r="D743" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E743" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -71771,7 +71771,7 @@
       </c>
       <c r="D750" s="23" t="n">
         <f aca="false">D745*D749/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E750" s="23" t="n">
         <f aca="false">E745*E749/1000</f>
@@ -72196,7 +72196,7 @@
       </c>
       <c r="D767" s="21" t="n">
         <f aca="false">D761/fx/D745*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E767" s="21" t="n">
         <f aca="false">E761/fx/E745*1000</f>
@@ -72593,11 +72593,11 @@
       </c>
       <c r="I781" s="29" t="n">
         <f aca="false">I778/I780</f>
-        <v>93.0410386142156</v>
+        <v>93.0410386142157</v>
       </c>
       <c r="J781" s="29" t="n">
         <f aca="false">J778/J780</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="782" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72629,7 +72629,7 @@
       </c>
       <c r="I782" s="25" t="n">
         <f aca="false">I781/H781-1</f>
-        <v>-0.0104556802106351</v>
+        <v>-0.010455680210635</v>
       </c>
       <c r="J782" s="25" t="n">
         <f aca="false">J781/I781-1</f>
@@ -72730,7 +72730,7 @@
       </c>
       <c r="D789" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E789" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -72898,7 +72898,7 @@
       </c>
       <c r="D796" s="23" t="n">
         <f aca="false">D791*D795/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E796" s="23" t="n">
         <f aca="false">E791*E795/1000</f>
@@ -73323,7 +73323,7 @@
       </c>
       <c r="D813" s="21" t="n">
         <f aca="false">D807/fx/D791*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E813" s="21" t="n">
         <f aca="false">E807/fx/E791*1000</f>
@@ -73724,7 +73724,7 @@
       </c>
       <c r="J827" s="29" t="n">
         <f aca="false">J824/J826</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73752,7 +73752,7 @@
       </c>
       <c r="H828" s="25" t="n">
         <f aca="false">H827/G827-1</f>
-        <v>0.0417547908160287</v>
+        <v>0.041754790816029</v>
       </c>
       <c r="I828" s="25" t="n">
         <f aca="false">I827/H827-1</f>
@@ -73857,7 +73857,7 @@
       </c>
       <c r="D835" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E835" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -74025,7 +74025,7 @@
       </c>
       <c r="D842" s="23" t="n">
         <f aca="false">D837*D841/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E842" s="23" t="n">
         <f aca="false">E837*E841/1000</f>
@@ -74450,7 +74450,7 @@
       </c>
       <c r="D859" s="21" t="n">
         <f aca="false">D853/fx/D837*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E859" s="21" t="n">
         <f aca="false">E853/fx/E837*1000</f>
@@ -74883,11 +74883,11 @@
       </c>
       <c r="I874" s="25" t="n">
         <f aca="false">I873/H873-1</f>
-        <v>0.0039988034792362</v>
+        <v>0.00399880347923665</v>
       </c>
       <c r="J874" s="25" t="n">
         <f aca="false">J873/I873-1</f>
-        <v>-0.0417070026045436</v>
+        <v>-0.0417070026045437</v>
       </c>
     </row>
     <row r="875" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -74984,7 +74984,7 @@
       </c>
       <c r="D881" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E881" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -75152,7 +75152,7 @@
       </c>
       <c r="D888" s="23" t="n">
         <f aca="false">D883*D887/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E888" s="23" t="n">
         <f aca="false">E883*E887/1000</f>
@@ -75577,7 +75577,7 @@
       </c>
       <c r="D905" s="21" t="n">
         <f aca="false">D899/fx/D883*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E905" s="21" t="n">
         <f aca="false">E899/fx/E883*1000</f>
@@ -75978,7 +75978,7 @@
       </c>
       <c r="J919" s="29" t="n">
         <f aca="false">J916/J918</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="920" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -76006,7 +76006,7 @@
       </c>
       <c r="H920" s="25" t="n">
         <f aca="false">H919/G919-1</f>
-        <v>0.0678539381452106</v>
+        <v>0.0678539381452108</v>
       </c>
       <c r="I920" s="25" t="n">
         <f aca="false">I919/H919-1</f>
@@ -76111,7 +76111,7 @@
       </c>
       <c r="D927" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E927" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -76279,7 +76279,7 @@
       </c>
       <c r="D934" s="23" t="n">
         <f aca="false">D929*D933/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E934" s="23" t="n">
         <f aca="false">E929*E933/1000</f>
@@ -76704,7 +76704,7 @@
       </c>
       <c r="D951" s="21" t="n">
         <f aca="false">D945/fx/D929*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E951" s="21" t="n">
         <f aca="false">E945/fx/E929*1000</f>
@@ -77101,11 +77101,11 @@
       </c>
       <c r="I965" s="29" t="n">
         <f aca="false">I962/I964</f>
-        <v>90.0463710777749</v>
+        <v>90.046371077775</v>
       </c>
       <c r="J965" s="29" t="n">
         <f aca="false">J962/J964</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="966" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77133,7 +77133,7 @@
       </c>
       <c r="H966" s="25" t="n">
         <f aca="false">H965/G965-1</f>
-        <v>0.0625936495599415</v>
+        <v>0.0625936495599417</v>
       </c>
       <c r="I966" s="25" t="n">
         <f aca="false">I965/H965-1</f>
@@ -77238,7 +77238,7 @@
       </c>
       <c r="D973" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E973" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -77406,7 +77406,7 @@
       </c>
       <c r="D980" s="23" t="n">
         <f aca="false">D975*D979/1000</f>
-        <v>9.94480366787716</v>
+        <v>9.94480366787715</v>
       </c>
       <c r="E980" s="23" t="n">
         <f aca="false">E975*E979/1000</f>
@@ -77831,7 +77831,7 @@
       </c>
       <c r="D997" s="21" t="n">
         <f aca="false">D991/fx/D975*1000</f>
-        <v>73.4578604462223</v>
+        <v>73.4578604462224</v>
       </c>
       <c r="E997" s="21" t="n">
         <f aca="false">E991/fx/E975*1000</f>
@@ -78232,7 +78232,7 @@
       </c>
       <c r="J1011" s="29" t="n">
         <f aca="false">J1008/J1010</f>
-        <v>87.664086010355</v>
+        <v>87.6640860103551</v>
       </c>
     </row>
     <row r="1012" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -78264,11 +78264,11 @@
       </c>
       <c r="I1012" s="25" t="n">
         <f aca="false">I1011/H1011-1</f>
-        <v>-0.028761050904341</v>
+        <v>-0.0287610509043407</v>
       </c>
       <c r="J1012" s="25" t="n">
         <f aca="false">J1011/I1011-1</f>
-        <v>-0.0788475020796176</v>
+        <v>-0.0788475020796177</v>
       </c>
     </row>
     <row r="1013" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/gce/dist/20261025_金像電模型_v0.1.1.xlsx
+++ b/gce/dist/20261025_金像電模型_v0.1.1.xlsx
@@ -6299,26 +6299,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6498,26 +6498,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6619,26 +6619,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6740,26 +6740,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6861,26 +6861,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6982,26 +6982,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -44355,7 +44355,7 @@
         <v>94</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>34</v>
@@ -44470,7 +44470,7 @@
         <v>53</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>34</v>
@@ -52868,7 +52868,7 @@
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">vg_pge26</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="C22" s="21" t="n">
         <f aca="false">PL!D87</f>
@@ -52876,7 +52876,7 @@
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">C22/B22-1</f>
-        <v>-0.340530413236349</v>
+        <v>-0.340530413236355</v>
       </c>
       <c r="E22" s="21" t="n">
         <f aca="false">PL!D133</f>
@@ -52884,7 +52884,7 @@
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">E22/B22-1</f>
-        <v>-0.340530413236349</v>
+        <v>-0.340530413236355</v>
       </c>
       <c r="G22" s="21" t="n">
         <f aca="false">PL!D179</f>
@@ -52892,7 +52892,7 @@
       </c>
       <c r="H22" s="17" t="n">
         <f aca="false">G22/B22-1</f>
-        <v>-0.340530413236349</v>
+        <v>-0.340530413236355</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>731</v>
@@ -53024,7 +53024,7 @@
       </c>
       <c r="B26" s="17" t="n">
         <f aca="false">vg_sh26</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">PL!D73</f>
@@ -53032,7 +53032,7 @@
       </c>
       <c r="D26" s="17" t="n">
         <f aca="false">C26-B26</f>
-        <v>-0.0746897693910072</v>
+        <v>-0.0746897693910082</v>
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">PL!D119</f>
@@ -53040,7 +53040,7 @@
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">E26-B26</f>
-        <v>-0.0746897693910072</v>
+        <v>-0.0746897693910082</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">PL!D165</f>
@@ -53048,7 +53048,7 @@
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">G26-B26</f>
-        <v>-0.0746897693910072</v>
+        <v>-0.0746897693910082</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>731</v>
